--- a/artfynd/A 55894-2022 artfynd.xlsx
+++ b/artfynd/A 55894-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55894-2022 artfynd.xlsx
+++ b/artfynd/A 55894-2022 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1996691</v>
+        <v>488249</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2412</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542077.0206128833</v>
+        <v>541996</v>
       </c>
       <c r="R2" t="n">
-        <v>7035630.517730736</v>
+        <v>7035483</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2012-09-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-09-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,12 +779,7 @@
         <v>1608743</v>
       </c>
       <c r="B3" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541851.7326411584</v>
+        <v>541852</v>
       </c>
       <c r="R3" t="n">
-        <v>7035519.709025216</v>
+        <v>7035520</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +844,9 @@
           <t>2012-09-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-09-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,53 +877,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1871726</v>
+        <v>96954783</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fullsundet, Jmt</t>
+          <t>Borgvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541926.0644626362</v>
+        <v>541846</v>
       </c>
       <c r="R4" t="n">
-        <v>7035489.805046132</v>
+        <v>7035519</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,22 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2012-09-24</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2012-09-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,53 +962,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Sofia Lundman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Åsa Stenman</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>488249</v>
+        <v>1871726</v>
       </c>
       <c r="B5" t="n">
-        <v>92505</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2412</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Philonotis fontana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541996.0652762823</v>
+        <v>541926</v>
       </c>
       <c r="R5" t="n">
-        <v>7035482.669150145</v>
+        <v>7035490</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,19 +1042,9 @@
           <t>2012-09-24</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2012-09-24</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,53 +1075,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2072567</v>
+        <v>96954782</v>
       </c>
       <c r="B6" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fullsundet, Jmt</t>
+          <t>Borgvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542076.9970391499</v>
+        <v>541844</v>
       </c>
       <c r="R6" t="n">
-        <v>7035632.307419288</v>
+        <v>7035528</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1209,22 +1140,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2012-09-24</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2012-09-24</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,35 +1160,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Sofia Lundman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Åsa Stenman</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96954782</v>
+        <v>97186732</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1295,10 +1207,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541843.5624233695</v>
+        <v>542038</v>
       </c>
       <c r="R7" t="n">
-        <v>7035527.65724796</v>
+        <v>7035512</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,22 +1237,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,65 +1257,64 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sofia Lundman</t>
+          <t>Andreas Bernhold</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sofia Lundman</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Andreas Bernhold</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96954783</v>
+        <v>1996691</v>
       </c>
       <c r="B8" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Borgvattnet, Jmt</t>
+          <t>Fullsundet, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>541845.908117341</v>
+        <v>542077</v>
       </c>
       <c r="R8" t="n">
-        <v>7035519.63272412</v>
+        <v>7035631</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1437,22 +1338,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-09-24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-09-24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,49 +1358,48 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sofia Lundman</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sofia Lundman</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Åsa Stenman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97186740</v>
+        <v>97186741</v>
       </c>
       <c r="B9" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1519,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>542084.1772215621</v>
+        <v>542076</v>
       </c>
       <c r="R9" t="n">
-        <v>7035631.50700511</v>
+        <v>7035640</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1552,19 +1442,9 @@
           <t>2021-10-07</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-10-07</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,53 +1475,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>97186741</v>
+        <v>2072567</v>
       </c>
       <c r="B10" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Borgvattnet, Jmt</t>
+          <t>Fullsundet, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>542075.0988635808</v>
+        <v>542077</v>
       </c>
       <c r="R10" t="n">
-        <v>7035640.337400475</v>
+        <v>7035632</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1665,22 +1540,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-10-07</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-09-24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-10-07</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-09-24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,71 +1560,61 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Andreas Bernhold</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Andreas Bernhold</t>
+          <t>Åsa Stenman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>Ecogain</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>97186738</v>
+        <v>97186740</v>
       </c>
       <c r="B11" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Borgvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>542088.5513551543</v>
+        <v>542084</v>
       </c>
       <c r="R11" t="n">
-        <v>7035605.609540779</v>
+        <v>7035632</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,19 +1644,9 @@
           <t>2021-10-07</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-10-07</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1832,15 +1677,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>97186734</v>
+        <v>97186739</v>
       </c>
       <c r="B12" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1848,21 +1688,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1872,10 +1712,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>542072.0919749284</v>
+        <v>542099</v>
       </c>
       <c r="R12" t="n">
-        <v>7035562.432110913</v>
+        <v>7035616</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1905,19 +1745,9 @@
           <t>2021-10-07</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-10-07</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1948,50 +1778,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>97186731</v>
+        <v>97186738</v>
       </c>
       <c r="B13" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Borgvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>542033.8076799668</v>
+        <v>542089</v>
       </c>
       <c r="R13" t="n">
-        <v>7035509.121601664</v>
+        <v>7035606</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2021,19 +1851,9 @@
           <t>2021-10-07</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-10-07</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2064,15 +1884,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>97186737</v>
+        <v>96954760</v>
       </c>
       <c r="B14" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2080,21 +1895,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221725</v>
+        <v>220093</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2104,10 +1919,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>542076.8081911793</v>
+        <v>542038</v>
       </c>
       <c r="R14" t="n">
-        <v>7035578.604524896</v>
+        <v>7035580</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2134,22 +1949,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-10-07</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-10-07</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,31 +1969,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Andreas Bernhold</t>
+          <t>Sofia Lundman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Andreas Bernhold</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>97186739</v>
+        <v>97186737</v>
       </c>
       <c r="B15" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,21 +1992,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>221725</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2220,10 +2016,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>542099.6223385311</v>
+        <v>542077</v>
       </c>
       <c r="R15" t="n">
-        <v>7035615.600485847</v>
+        <v>7035579</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2253,19 +2049,9 @@
           <t>2021-10-07</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2021-10-07</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2296,37 +2082,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>97186732</v>
+        <v>97186734</v>
       </c>
       <c r="B16" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2336,10 +2117,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>542037.8047293366</v>
+        <v>542072</v>
       </c>
       <c r="R16" t="n">
-        <v>7035511.859295552</v>
+        <v>7035562</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2369,19 +2150,9 @@
           <t>2021-10-07</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2021-10-07</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 55894-2022 artfynd.xlsx
+++ b/artfynd/A 55894-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/488249</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1608743</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96954783</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1871726</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1169,6 +1194,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96954782</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1270,6 +1300,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97186732</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1996691</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1472,6 +1512,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97186741</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1573,6 +1618,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2072567</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1674,6 +1724,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97186740</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1775,6 +1830,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97186739</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1881,6 +1941,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97186738</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1978,6 +2043,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96954760</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2079,6 +2149,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97186737</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2180,8 +2255,30 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97186734</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>